--- a/بنيان/اصناف/New folder/03_ERPNext_UOM.xlsx
+++ b/بنيان/اصناف/New folder/03_ERPNext_UOM.xlsx
@@ -1,133 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UOM" sheetId="1" r:id="R5b99305843b04f2f"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dark\work\بنيان\اصناف\New folder\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A168ED9B-72D5-432E-B74B-FA286ABA3572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="UOM" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+  <si>
+    <t>uom_name</t>
+  </si>
+  <si>
+    <t>must_be_whole_number</t>
+  </si>
+  <si>
+    <t>enabled</t>
+  </si>
+  <si>
+    <t>symbol</t>
+  </si>
+  <si>
+    <t>متر</t>
+  </si>
+  <si>
+    <t>عود</t>
+  </si>
+  <si>
+    <t>لفه</t>
+  </si>
+  <si>
+    <t>كيس</t>
+  </si>
+  <si>
+    <t>كرتونه</t>
+  </si>
+  <si>
+    <t>علبه</t>
+  </si>
+  <si>
+    <t>تي</t>
+  </si>
+  <si>
+    <t>قطعه</t>
+  </si>
+  <si>
+    <t>شكاره</t>
+  </si>
+  <si>
+    <t>وصله</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF202124"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF33363A"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="5">
-    <x:border/>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD9D9D9"/>
-      </x:right>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD9D9D9"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD9D9D9"/>
-      </x:right>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD9D9D9"/>
-      </x:left>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="11">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202124"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33363A"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="5">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_03_ERPNext_UOM_xlsx" displayName="T_03_ERPNext_UOM_xlsx" ref="A1:D2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="uom_name"/>
-    <x:tableColumn id="2" name="must_be_whole_number"/>
-    <x:tableColumn id="3" name="enabled"/>
-    <x:tableColumn id="4" name="symbol"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="T_03_ERPNext_UOM_xlsx" displayName="T_03_ERPNext_UOM_xlsx" ref="A1:D58" totalsRowShown="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="uom_name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="must_be_whole_number"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="enabled"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="symbol"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -318,54 +385,230 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FFFF7A00"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="7" t="str">
-        <x:v>uom_name</x:v>
-      </x:c>
-      <x:c r="B1" s="7" t="str">
-        <x:v>must_be_whole_number</x:v>
-      </x:c>
-      <x:c r="C1" s="7" t="str">
-        <x:v>enabled</x:v>
-      </x:c>
-      <x:c r="D1" s="7" t="str">
-        <x:v>symbol</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="8" t="str">
-        <x:v>قطعة</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>قطعة</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca16c8ccc7d84fce"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF7A00"/>
+  </sheetPr>
+  <dimension ref="A1:D58"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="33.950000000000003" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="24" customHeight="1">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="24" customHeight="1">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="24" customHeight="1">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="24" customHeight="1">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="24" customHeight="1">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="24" customHeight="1">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="24" customHeight="1">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1"/>
+    <row r="13" spans="1:4" ht="24" customHeight="1"/>
+    <row r="14" spans="1:4" ht="24" customHeight="1"/>
+    <row r="15" spans="1:4" ht="24" customHeight="1"/>
+    <row r="16" spans="1:4" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1"/>
+    <row r="28" ht="24" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1"/>
+    <row r="30" ht="24" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1"/>
+    <row r="32" ht="24" customHeight="1"/>
+    <row r="33" ht="24" customHeight="1"/>
+    <row r="34" ht="24" customHeight="1"/>
+    <row r="35" ht="24" customHeight="1"/>
+    <row r="36" ht="24" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1"/>
+    <row r="38" ht="24" customHeight="1"/>
+    <row r="39" ht="24" customHeight="1"/>
+    <row r="40" ht="24" customHeight="1"/>
+    <row r="41" ht="24" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1"/>
+    <row r="43" ht="24" customHeight="1"/>
+    <row r="44" ht="24" customHeight="1"/>
+    <row r="45" ht="24" customHeight="1"/>
+    <row r="46" ht="24" customHeight="1"/>
+    <row r="47" ht="24" customHeight="1"/>
+    <row r="48" ht="24" customHeight="1"/>
+    <row r="49" ht="24" customHeight="1"/>
+    <row r="50" ht="24" customHeight="1"/>
+    <row r="51" ht="24" customHeight="1"/>
+    <row r="52" ht="24" customHeight="1"/>
+    <row r="53" ht="24" customHeight="1"/>
+    <row r="54" ht="24" customHeight="1"/>
+    <row r="55" ht="24" customHeight="1"/>
+    <row r="56" ht="24" customHeight="1"/>
+    <row r="57" ht="24" customHeight="1"/>
+    <row r="58" ht="24" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>